--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486768_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486768_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.980700000000001</v>
+        <v>9.088200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.039199999999999</v>
+        <v>8.246</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9415</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>5.5532</v>
@@ -610,13 +610,13 @@
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0647</v>
+        <v>1.1722</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1648</v>
+        <v>0.3717</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8999</v>
+        <v>0.8006</v>
       </c>
       <c r="V2" t="n">
         <v>2.1698</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2916</v>
+        <v>4.2431</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2268</v>
+        <v>4.0542</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0648</v>
+        <v>0.1889</v>
       </c>
       <c r="G3" t="n">
         <v>3.2649</v>
@@ -688,13 +688,13 @@
         <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5792</v>
+        <v>0.3724</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0761</v>
+        <v>-0.2487</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4969</v>
+        <v>0.6211</v>
       </c>
       <c r="V3" t="n">
         <v>1.1851</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0229</v>
+        <v>4.1661</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5189</v>
+        <v>2.7118</v>
       </c>
       <c r="F4" t="n">
-        <v>1.504</v>
+        <v>1.4543</v>
       </c>
       <c r="G4" t="n">
         <v>1.194</v>
@@ -766,13 +766,13 @@
         <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3641</v>
+        <v>0.7791</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6071</v>
+        <v>0.5857</v>
       </c>
       <c r="U4" t="n">
-        <v>0.243</v>
+        <v>0.1934</v>
       </c>
       <c r="V4" t="n">
         <v>1.2277</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GONZALEZ GRANDE</t>
+          <t>J. MORENO CASTRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8025</v>
+        <v>0.5881</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1872</v>
+        <v>-0.4116</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9897</v>
+        <v>0.9996</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9404</v>
+        <v>-0.0944</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6126</v>
+        <v>-0.5104</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3278</v>
+        <v>0.416</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.064</v>
+        <v>-0.6458</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2674</v>
+        <v>-0.6481</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2035</v>
+        <v>0.0023</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8764</v>
+        <v>0.5514</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3451</v>
+        <v>0.1377</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5313</v>
+        <v>0.4137</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5446</v>
+        <v>0.7723</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7855</v>
+        <v>0.524</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1784</v>
+        <v>0.2343</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6071</v>
+        <v>0.2897</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6565</v>
+        <v>-0.6138</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2856</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7035</v>
+        <v>0.4677</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5103</v>
+        <v>-0.8205</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2138</v>
+        <v>1.2883</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6167</v>
@@ -922,13 +922,13 @@
         <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0426</v>
+        <v>0.8068</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4407</v>
+        <v>0.1305</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6018</v>
+        <v>0.6763</v>
       </c>
       <c r="V6" t="n">
         <v>0.8568</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MORENO CASTRO</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5659</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2599</v>
+        <v>-1.6701</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8258</v>
+        <v>1.5721</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0944</v>
+        <v>0.2329</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5104</v>
+        <v>0.0136</v>
       </c>
       <c r="I7" t="n">
-        <v>0.416</v>
+        <v>0.2193</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6458</v>
+        <v>-0.5253</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6481</v>
+        <v>0.0828</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0023</v>
+        <v>-0.6081</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5514</v>
+        <v>0.7582</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1377</v>
+        <v>-0.0692</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4137</v>
+        <v>0.8274</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7723</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q7" t="n">
+        <v>-0.9654</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.1794</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.2346</v>
+      </c>
+      <c r="V7" t="n">
         <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.7723</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.5018</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.3859</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.1159</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.6138</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0351</v>
+        <v>-0.2984</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0536</v>
+        <v>-1.5155</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0185</v>
+        <v>1.2171</v>
       </c>
       <c r="G8" t="n">
         <v>-1.316</v>
@@ -1078,13 +1078,13 @@
         <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3734</v>
+        <v>1.1101</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1029</v>
+        <v>0.641</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2705</v>
+        <v>0.4691</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2856</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>R. GONZALEZ GRANDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2801</v>
+        <v>-0.5075</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.877</v>
+        <v>-1.373</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5969</v>
+        <v>0.8655</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2329</v>
+        <v>-0.9404</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0136</v>
+        <v>-0.6126</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2193</v>
+        <v>-0.3278</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5253</v>
+        <v>-0.064</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0828</v>
+        <v>-0.2674</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6081</v>
+        <v>0.2035</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7582</v>
+        <v>-0.8764</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0692</v>
+        <v>-0.3451</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8274</v>
+        <v>-0.5313</v>
       </c>
       <c r="P9" t="n">
         <v>-0.3862</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5792</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1268</v>
+        <v>1.4755</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3863</v>
+        <v>0.9926</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2595</v>
+        <v>0.4829</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3709</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. LUIS QUINTERO</t>
+          <t>M. GONZALEZ-MONJE PEREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9508</v>
+        <v>-1.439</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4721</v>
+        <v>-1.6119</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5213</v>
+        <v>0.1729</v>
       </c>
       <c r="G10" t="n">
-        <v>0.528</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3439</v>
+        <v>-0.2759</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8719</v>
+        <v>0.3639</v>
       </c>
       <c r="J10" t="n">
-        <v>2.495</v>
+        <v>-0.263</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9327</v>
+        <v>0.3451</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5623</v>
+        <v>-0.6081</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.967</v>
+        <v>0.351</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.2766</v>
+        <v>-0.6211</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3096</v>
+        <v>0.972</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.7031</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.827</v>
+        <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1239</v>
+        <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6796</v>
+        <v>0.531</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5163</v>
+        <v>0.2963</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1634</v>
+        <v>0.2347</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4554</v>
+        <v>-0.8995</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6565</v>
+        <v>0.2856</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7989</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. GONZALEZ-MONJE PEREZ</t>
+          <t>P. RODRIGUEZ FAJARDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2347</v>
+        <v>-2.1509</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1842</v>
+        <v>-0.7127</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0506</v>
+        <v>-1.4382</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08799999999999999</v>
+        <v>-2.134</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2759</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3639</v>
+        <v>-1.327</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.263</v>
+        <v>-0.4365</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3451</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6081</v>
+        <v>-1.2162</v>
       </c>
       <c r="M11" t="n">
-        <v>0.351</v>
+        <v>-1.6975</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6211</v>
+        <v>-1.5867</v>
       </c>
       <c r="O11" t="n">
-        <v>0.972</v>
+        <v>-0.1108</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.7723</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2648</v>
+        <v>0.1102</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.276</v>
+        <v>-0.2761</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0112</v>
+        <v>0.3864</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8995</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1851</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ FAJARDO</t>
+          <t>C. LUIS QUINTERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9619</v>
+        <v>-2.879</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1264</v>
+        <v>-2.5063</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8356</v>
+        <v>-0.3726</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.134</v>
+        <v>0.528</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-1.3439</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.327</v>
+        <v>1.8719</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4365</v>
+        <v>2.495</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.9327</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2162</v>
+        <v>1.5623</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6975</v>
+        <v>-1.967</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5867</v>
+        <v>-2.2766</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1108</v>
+        <v>0.3096</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7723</v>
+        <v>-2.7031</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-4.827</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7723</v>
+        <v>2.1239</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7008</v>
+        <v>1.7515</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6898</v>
+        <v>0.482</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0109</v>
+        <v>1.2694</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8995</v>
+        <v>-2.4554</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8995</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.9045</v>
+        <v>11.1803</v>
       </c>
       <c r="E13" t="n">
-        <v>4.114199999999999</v>
+        <v>4.390400000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>6.790100000000002</v>
+        <v>6.790100000000001</v>
       </c>
       <c r="G13" t="n">
         <v>5.759500000000003</v>
@@ -1447,10 +1447,10 @@
         <v>10.0073</v>
       </c>
       <c r="L13" t="n">
-        <v>3.832400000000001</v>
+        <v>3.8324</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.080100000000002</v>
+        <v>-8.0801</v>
       </c>
       <c r="N13" t="n">
         <v>-14.4886</v>
@@ -1468,16 +1468,16 @@
         <v>14.4808</v>
       </c>
       <c r="S13" t="n">
-        <v>8.411900000000001</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7537</v>
+        <v>3.0299</v>
       </c>
       <c r="U13" t="n">
-        <v>5.6583</v>
+        <v>5.6582</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3709000000000002</v>
+        <v>-0.3708999999999998</v>
       </c>
       <c r="W13" t="n">
         <v>4.897899999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9633</v>
+        <v>3.3387</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4753</v>
+        <v>2.3376</v>
       </c>
       <c r="F14" t="n">
-        <v>0.488</v>
+        <v>1.0011</v>
       </c>
       <c r="G14" t="n">
         <v>2.5001</v>
@@ -1546,13 +1546,13 @@
         <v>3.0892</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2097</v>
+        <v>-0.8343</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9095</v>
+        <v>-0.2281</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1192</v>
+        <v>-0.6062</v>
       </c>
       <c r="V14" t="n">
         <v>-0.451</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8779</v>
+        <v>2.4791</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3426</v>
+        <v>1.7563</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5352</v>
+        <v>0.7228</v>
       </c>
       <c r="G15" t="n">
         <v>2.9481</v>
@@ -1624,13 +1624,13 @@
         <v>3.0892</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2633</v>
+        <v>-0.662</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4347</v>
+        <v>-1.021</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1715</v>
+        <v>0.359</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9553</v>
+        <v>1.5385</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1793</v>
+        <v>2.6964</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.224</v>
+        <v>-1.1579</v>
       </c>
       <c r="G16" t="n">
         <v>-2.252</v>
@@ -1702,13 +1702,13 @@
         <v>3.0892</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8863</v>
+        <v>-1.3031</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.6556</v>
+        <v>-1.1385</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2307</v>
+        <v>-0.1647</v>
       </c>
       <c r="V16" t="n">
         <v>2.0044</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1649</v>
+        <v>-0.5443</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4501</v>
+        <v>0.657</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.615</v>
+        <v>-1.2013</v>
       </c>
       <c r="G17" t="n">
         <v>1.2584</v>
@@ -1780,13 +1780,13 @@
         <v>1.5446</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3238</v>
+        <v>-0.7032</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6898</v>
+        <v>-0.483</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6339</v>
+        <v>-0.2203</v>
       </c>
       <c r="V17" t="n">
         <v>-1.6787</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DELICADO DOMINGUEZ</t>
+          <t>E. BUENO KNUTSEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1888</v>
+        <v>-2.1851</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0165</v>
+        <v>-2.445</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2053</v>
+        <v>0.2599</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1533</v>
+        <v>-2.5699</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7035</v>
+        <v>-0.8902</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8568</v>
+        <v>-1.6796</v>
       </c>
       <c r="J18" t="n">
-        <v>1.317</v>
+        <v>-1.962</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3938</v>
+        <v>0.1448</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-2.1068</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4703</v>
+        <v>-0.6079</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6903</v>
+        <v>-1.0351</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.78</v>
+        <v>0.4272</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6017</v>
+        <v>-0.593</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0824</v>
+        <v>-0.483</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5193</v>
+        <v>-0.11</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8995</v>
+        <v>0.2055</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4128</v>
+        <v>0.2055</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. BUENO KNUTSEN</t>
+          <t>R. SANCHEZ CASTILLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6291</v>
+        <v>-2.8311</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6518</v>
+        <v>-2.7056</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0227</v>
+        <v>-0.1254</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5699</v>
+        <v>-2.7305</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8902</v>
+        <v>-0.4903</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6796</v>
+        <v>-2.2403</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.962</v>
+        <v>0.0571</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1448</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.1068</v>
+        <v>-0.764</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6079</v>
+        <v>-2.7876</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0351</v>
+        <v>-1.3113</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4272</v>
+        <v>-1.4763</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="Q19" t="n">
+        <v>-1.9308</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.3169</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.7723</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1.1175</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="X19" t="n">
         <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.7723</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-1.0371</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-0.6898</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.3472</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.2055</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.2055</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. SANCHEZ CASTILLO</t>
+          <t>A. DELICADO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3496</v>
+        <v>-2.9075</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9125</v>
+        <v>-0.2938</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4371</v>
+        <v>-2.6137</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7305</v>
+        <v>-0.1533</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4903</v>
+        <v>0.7035</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2403</v>
+        <v>-0.8568</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0571</v>
+        <v>1.317</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8211000000000001</v>
+        <v>1.3938</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.764</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7876</v>
+        <v>-1.4703</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3113</v>
+        <v>-0.6903</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4763</v>
+        <v>-0.78</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3862</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3169</v>
+        <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2908</v>
+        <v>-0.117</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3244</v>
+        <v>-0.2279</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0335</v>
+        <v>0.1109</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2856</v>
+        <v>-0.8995</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2856</v>
+        <v>1.5133</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.4128</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.368600000000001</v>
+        <v>-7.7244</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.6896</v>
+        <v>-8.792999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.321</v>
+        <v>1.0686</v>
       </c>
       <c r="G21" t="n">
         <v>-4.7603</v>
@@ -2092,13 +2092,13 @@
         <v>2.3169</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.0028</v>
+        <v>-1.3586</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8557</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.147</v>
+        <v>-0.3994</v>
       </c>
       <c r="V21" t="n">
         <v>0.9046</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.9045</v>
+        <v>-8.836099999999998</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.790100000000001</v>
+        <v>-6.790099999999997</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.1145</v>
+        <v>-2.0459</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.7594</v>
+        <v>-5.759399999999999</v>
       </c>
       <c r="H22" t="n">
         <v>4.481299999999999</v>
@@ -2149,7 +2149,7 @@
         <v>14.4884</v>
       </c>
       <c r="L22" t="n">
-        <v>-6.408099999999999</v>
+        <v>-6.4081</v>
       </c>
       <c r="M22" t="n">
         <v>-13.8397</v>
@@ -2170,13 +2170,13 @@
         <v>17.3768</v>
       </c>
       <c r="S22" t="n">
-        <v>-8.412100000000001</v>
+        <v>-6.343500000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-5.658099999999999</v>
+        <v>-5.6582</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.7537</v>
+        <v>-0.6855</v>
       </c>
       <c r="V22" t="n">
         <v>0.3708999999999998</v>
